--- a/انجليزي ترم ثاني.xlsx
+++ b/انجليزي ترم ثاني.xlsx
@@ -7198,7 +7198,7 @@
         <v>24</v>
       </c>
       <c r="K23">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="24">
@@ -7230,7 +7230,7 @@
         <v>26</v>
       </c>
       <c r="K24">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="25">
@@ -7294,7 +7294,7 @@
         <v>30</v>
       </c>
       <c r="K26">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="27">
@@ -7361,7 +7361,7 @@
         <v>18</v>
       </c>
       <c r="K28">
-        <v>27</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="29">
@@ -7393,7 +7393,7 @@
         <v>27</v>
       </c>
       <c r="K29">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="30">
@@ -7425,7 +7425,7 @@
         <v>32</v>
       </c>
       <c r="K30">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="31">
@@ -7457,7 +7457,7 @@
         <v>22</v>
       </c>
       <c r="K31">
-        <v>31</v>
+        <v>31.5</v>
       </c>
     </row>
   </sheetData>
@@ -7541,7 +7541,7 @@
         <v>29</v>
       </c>
       <c r="K2">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="3">
@@ -7573,7 +7573,7 @@
         <v>25</v>
       </c>
       <c r="K3">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="4">
@@ -7605,7 +7605,7 @@
         <v>14</v>
       </c>
       <c r="K4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -7637,7 +7637,7 @@
         <v>22</v>
       </c>
       <c r="K5">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="6">
@@ -7669,7 +7669,7 @@
         <v>16</v>
       </c>
       <c r="K6">
-        <v>25</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="7">
@@ -7701,7 +7701,7 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="8">
@@ -7733,7 +7733,7 @@
         <v>13</v>
       </c>
       <c r="K8">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -7800,7 +7800,7 @@
         <v>21</v>
       </c>
       <c r="K10">
-        <v>29</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="11">
@@ -7963,7 +7963,7 @@
         <v>18</v>
       </c>
       <c r="K15">
-        <v>26</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="16">
@@ -7995,7 +7995,7 @@
         <v>23</v>
       </c>
       <c r="K16">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="17">
@@ -8059,7 +8059,7 @@
         <v>21</v>
       </c>
       <c r="K18">
-        <v>30</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="19">
